--- a/files/pre-dea.xlsx
+++ b/files/pre-dea.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nahue\Desktop\basura\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nahue\Desktop\UB\DEA_mates_info_UB\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE91166-B36D-4C24-8673-BB2A8F0279E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0255AF01-73B8-483A-9944-4FD904FFD729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{600831CA-5CE0-4E56-B20F-FFA9C475C658}"/>
+    <workbookView xWindow="-100" yWindow="-100" windowWidth="24172" windowHeight="14475" xr2:uid="{600831CA-5CE0-4E56-B20F-FFA9C475C658}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>Universitat Destí</t>
   </si>
@@ -69,6 +69,27 @@
   </si>
   <si>
     <t>comentaris</t>
+  </si>
+  <si>
+    <t>Matemàtiques</t>
+  </si>
+  <si>
+    <t>Informàtica</t>
+  </si>
+  <si>
+    <t>Mates-Info</t>
+  </si>
+  <si>
+    <t>Mates-ADE</t>
+  </si>
+  <si>
+    <t>Mates-Física</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grau:  </t>
+  </si>
+  <si>
+    <t>(escull un)</t>
   </si>
 </sst>
 </file>
@@ -280,7 +301,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -300,6 +321,15 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -324,16 +354,60 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -351,6 +425,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -671,45 +762,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3CC9E4A-5604-474A-97C2-14F628253A07}">
   <dimension ref="A1:I19"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.4609375" customWidth="1"/>
     <col min="2" max="7" width="16.765625" customWidth="1"/>
     <col min="9" max="9" width="10.3046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" ht="14.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="23"/>
+      <c r="D1" s="13"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="16" t="s">
+      <c r="C2" s="20"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="17"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="21" t="s">
+      <c r="F2" s="20"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="20"/>
+    <row r="3" spans="1:9" ht="14.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="23"/>
       <c r="B3" s="10" t="s">
         <v>3</v>
       </c>
@@ -728,10 +819,10 @@
       <c r="G3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+    </row>
+    <row r="4" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="str">
         <f>IF(B4="","",1)</f>
         <v/>
@@ -745,7 +836,7 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="str">
         <f>IF(OR(A4="",B5=""),"",A4+1)</f>
         <v/>
@@ -759,9 +850,9 @@
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="str">
-        <f t="shared" ref="A6:A16" si="0">IF(OR(A5="",B6=""),"",A5+1)</f>
+        <f t="shared" ref="A6:A14" si="0">IF(OR(A5="",B6=""),"",A5+1)</f>
         <v/>
       </c>
       <c r="B6" s="4"/>
@@ -773,7 +864,7 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -787,7 +878,7 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -801,7 +892,7 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -871,88 +962,100 @@
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:9" ht="14.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A15" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-    </row>
-    <row r="17" spans="1:9" ht="14.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="13" t="s">
+      <c r="B14" s="6"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" spans="1:9" ht="14.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-    </row>
-    <row r="18" spans="1:9" ht="14.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="15"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-    </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="15"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="28"/>
+    </row>
+    <row r="16" spans="1:9" ht="14.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="18"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="30"/>
+    </row>
+    <row r="17" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="31"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="33"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B18" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="14.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B19" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="27" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="I2:I3"/>
-    <mergeCell ref="A17:I19"/>
+    <mergeCell ref="A15:I17"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="A2:A3"/>
